--- a/data/источники.xlsx
+++ b/data/источники.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Источники" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Источники'!$A$3:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Источники'!$A$3:$H$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1413,8 +1413,344 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>National Institute on Aging (NIA, NIH)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nia.nih.gov/</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Гос. научная организация</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Физиология/Психология/Здоровье</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Профильный институт NIH (США) по исследованию старения — биология, физиология, психология, публикации</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Российская ассоциация геронтологов и гериатров (РАГГ)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>https://rosagg.ru/</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Профессиональная ассоциация</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Физиология/Здоровье</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Профессиональное сообщество врачей-гериатров РФ, клинические рекомендации по гериатрии</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Геронтологическое общество при РАН</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>http://gersociety.ru/</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Профессиональная ассоциация</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Физиология</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Научное сообщество геронтологов при Российской академии наук</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Долголетие Подмосковья</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>https://dolgoletie.mosreg.ru/</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Гос./муниципальная программа</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Досуг/Спорт</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Региональная программа Московской области — кружки, спорт, обучение для старшего поколения</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>CDC — Physical Activity for Older Adults</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/physical-activity-basics/adding-older-adults/index.html</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Гос. информационный портал</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Спорт/Здоровье</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Официальные рекомендации по физической активности для пожилых от CDC (США)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>American College of Sports Medicine (ACSM)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>https://acsm.org/</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Профессиональная ассоциация</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Спорт</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Ведущая ассоциация спортивной медицины, рекомендации по физактивности для старшего возраста</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>APA Division 20 — Adult Development and Aging</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.apadivisions.org/division-20/</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Профессиональная ассоциация</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Психология</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Подразделение Американской психологической ассоциации по психологии взрослого развития и старения</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>European Geriatric Medicine Society (EuGMS)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.eugms.org/</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Профессиональная ассоциация</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Физиология/Здоровье</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Объединение национальных гериатрических обществ Европы (39 стран), конгрессы и журнал</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:H24"/>
+  <autoFilter ref="A3:H32"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>

--- a/data/источники.xlsx
+++ b/data/источники.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Источники" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Источники'!$A$3:$H$32</definedName>
@@ -564,7 +564,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>На рассмотрении</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">

--- a/data/источники.xlsx
+++ b/data/источники.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Источники" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Источники" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Источники'!$A$3:$H$32</definedName>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1749,6 +1749,300 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>International Psychogeriatric Association (IPA)</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ipa-online.org/</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Профессиональная ассоциация</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Психология</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Международная мультидисциплинарная ассоциация по психическому здоровью пожилых людей, издаёт журнал International Psychogeriatrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>ФГБУ «НМИЦ ТПМ» Минздрава России — рекомендации по физической активности</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>https://gnicpm.ru/articles/zdorovyj-obraz-zhizni/rekomendaczii-po-fizicheskoj-aktivnosti-dlya-lyudej-starshe-65-let.html</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Гос. информационный портал</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Спорт/Здоровье</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Официальные рекомендации по физической активности для людей старше 65 лет от профильного центра Минздрава РФ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Национальный психологический журнал</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>https://npsyj.ru/</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Научный журнал</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Психология</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Рецензируемый журнал факультета психологии МГУ, есть материалы по возрастной психологии и старению</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>PMC — Engagement in leisure activities and depression in older adults (Health and Retirement Study)</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC8850653/</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Научная статья</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Досуг/Психология</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Лонгитюдное исследование связи досуговой активности и депрессии у пожилых (19 134 участника старше 50 лет, Health and Retirement Study)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>PMC — Cognitive and psychoemotional changes in menopausal transition</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/PMC9978879/</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Научная статья</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Физиология/Психология</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Когнитивные и психоэмоциональные изменения в период менопаузального перехода и постменопаузы</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Вектор науки. Педагогика, психология — Возрастные изменения когнитивных функций у пожилых людей</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>https://vektornaukipedagogika.ru/jour/article/view/236/ru_RU</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Научный журнал</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Психология</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Рецензируемая статья о возрастных изменениях когнитивных функций у пожилых людей</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Объясняем.рф — программы активного долголетия в регионах России</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>https://xn--90aivcdt6dxbc.xn--p1ai/articles/useful/divan-ne-drug-pensioneru-kak-uluchshayut-kachestvo-zhizni-pozhilykh-programmy-aktivnogo-dolgoletiya-/</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Гос. информационный портал</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Досуг/Спорт</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Официальный государственный портал о региональных программах активного долголетия (нацпроект «Демография»/«Семья»)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:H32"/>
   <mergeCells count="1">

--- a/data/источники.xlsx
+++ b/data/источники.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2043,342 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>National Institute on Aging — Participating in Activities You Enjoy As You Age</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nia.nih.gov/health/healthy-aging/participating-activities-you-enjoy-you-age</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Гос. научная организация</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Досуг/Здоровье</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Практические рекомендации NIA о пользе хобби и досуговой активности для здоровья в пожилом возрасте</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Oasis Institute</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oasisnet.org/</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>НКО</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Досуг/Здоровье</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Крупная американская некоммерческая организация по активному долголетию (обучение, физкультура, волонтёрство), более 40 лет работы, 40 городов США</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>AmeriCorps Seniors</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.americorps.gov/serve/americorps-seniors</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Гос./муниципальная программа</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Досуг</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Национальная гос. программа волонтёрства США для людей 55+ (наставничество, помощь пожилым и соседям) — источник идей про востребованность через посильный труд</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>International Association of Gerontology and Geriatrics (IAGG)</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>https://iagg.site/</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Профессиональная ассоциация</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Физиология/Психология</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Международная зонтичная ассоциация геронтологических обществ (с 1950 г., статус НКО при ООН), объединяет региональные организации по всему миру</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>WHO — Менопауза (фактлист)</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.who.int/ru/news-room/fact-sheets/detail/menopause</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Международная организация</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Физиология</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Официальный фактлист ВОЗ о физиологии менопаузы/постменопаузы и связанных рисках для здоровья женщин</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>АиФ — Кризис старшего возраста: как пережить стресс при выходе на пенсию</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>https://aif.ru/health/psychologic/krizis_starshego_vozrasta_kak_perezhit_pensionnyy_stress</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Информационный портал</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Психология</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Научно-популярный разбор психологического кризиса и стресса при выходе на пенсию в крупном общественно-политическом издании</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Поиск (poisknews.ru) — перестройка мозга в возрасте 50–75 лет</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>https://poisknews.ru/nejrobiologiya/uchyonye-obnaruzhili-masshtabnuyu-perestrojku-mozga-v-vozraste-ot-50-do-75-let/</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Информационный портал (научные новости)</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Физиология</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Научно-популярное изложение исследования (Science, 2025) о клеточной перестройке мозга в возрасте 50–75 лет</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Т—Ж — Программы активного долголетия в регионах России</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>https://t-j.ru/short/dolgoletie-regiony/</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Информационный портал</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Досуг/Спорт</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>На рассмотрении</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Обзор региональных программ активного долголетия по России; издание принадлежит Тинькофф Банку — учитывать коммерческий уклон</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:H32"/>
   <mergeCells count="1">
